--- a/Template Import/AR Claim RE Template Service.xlsx
+++ b/Template Import/AR Claim RE Template Service.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MSIG\pregolive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB37CCB-3F12-4F96-ADF8-1F330121E9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A535AD3F-0C26-4150-86BC-B44AB01F7082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="13656" xr2:uid="{E44AA624-969E-4C5F-BCC1-7F47ABB06A31}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E44AA624-969E-4C5F-BCC1-7F47ABB06A31}"/>
   </bookViews>
   <sheets>
     <sheet name="Head" sheetId="2" r:id="rId1"/>
     <sheet name="Line" sheetId="1" r:id="rId2"/>
+    <sheet name="CUSTOMER + PRODUCT" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -418,7 +419,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
   <si>
     <t>ParentKey</t>
   </si>
@@ -520,6 +521,243 @@
   </si>
   <si>
     <t>PolicyNO</t>
+  </si>
+  <si>
+    <t>RE-Facutative</t>
+  </si>
+  <si>
+    <t>ສຳຮອງສິນທົດແທນ - ປະກັນໄພຕໍ່  - ສັນຍາປະກັນໄພຕໍ່ພິເສດ</t>
+  </si>
+  <si>
+    <t>ສຳຮອງສິນທົດແທນ - ປະກັນໄພຕໍ່  - ສັນຍາປະກັນໄພຕໍ່ອື່ນໆ</t>
+  </si>
+  <si>
+    <t>RE-Treaty</t>
+  </si>
+  <si>
+    <t>ສຳຮອງສິນທົດແທນ - ປະກັນໄພຕໍ່  - ສັນຍາປະກັນໄພຕໍ່ພັນທະ</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRODUCT </t>
+  </si>
+  <si>
+    <t>604.56.02</t>
+  </si>
+  <si>
+    <t>604.56.03</t>
+  </si>
+  <si>
+    <t>604.56.04</t>
+  </si>
+  <si>
+    <t>604.56.05</t>
+  </si>
+  <si>
+    <t>604.56.06</t>
+  </si>
+  <si>
+    <t>604.56.07</t>
+  </si>
+  <si>
+    <t>604.56.08</t>
+  </si>
+  <si>
+    <t>604.56.09</t>
+  </si>
+  <si>
+    <t>604.56.10</t>
+  </si>
+  <si>
+    <t>604.56.11</t>
+  </si>
+  <si>
+    <t>604.56.12</t>
+  </si>
+  <si>
+    <t>604.56.13</t>
+  </si>
+  <si>
+    <t>604.57.02</t>
+  </si>
+  <si>
+    <t>604.57.03</t>
+  </si>
+  <si>
+    <t>604.57.04</t>
+  </si>
+  <si>
+    <t>604.57.05</t>
+  </si>
+  <si>
+    <t>604.57.06</t>
+  </si>
+  <si>
+    <t>604.57.07</t>
+  </si>
+  <si>
+    <t>604.57.08</t>
+  </si>
+  <si>
+    <t>604.57.09</t>
+  </si>
+  <si>
+    <t>604.57.10</t>
+  </si>
+  <si>
+    <t>604.57.11</t>
+  </si>
+  <si>
+    <t>604.57.12</t>
+  </si>
+  <si>
+    <t>604.57.13</t>
+  </si>
+  <si>
+    <t>604.58.02</t>
+  </si>
+  <si>
+    <t>604.58.03</t>
+  </si>
+  <si>
+    <t>604.58.04</t>
+  </si>
+  <si>
+    <t>604.58.05</t>
+  </si>
+  <si>
+    <t>604.58.06</t>
+  </si>
+  <si>
+    <t>604.58.07</t>
+  </si>
+  <si>
+    <t>604.58.08</t>
+  </si>
+  <si>
+    <t>604.58.09</t>
+  </si>
+  <si>
+    <t>604.58.10</t>
+  </si>
+  <si>
+    <t>604.58.11</t>
+  </si>
+  <si>
+    <t>604.58.12</t>
+  </si>
+  <si>
+    <t>604.58.13</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ-ລົດ-ພາກບັງຄັບ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ-ລົດ-ພາກສະໝັກໃຈ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ-ອັກຄີໄພ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ-ຂົນສົ່ງ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ- ອຫ ສ່ວນບຸກຄົນ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ-ສຸຂະພາບ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ-ທ່ອງທ່ຽວ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ-ຊັບສິນ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ- ຄສ ຮອບດ້ານ ອກ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ-ວິສະວະກຳ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ-ສິນເຊື່ອ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ- ຄສ ອື່ນໆ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ-ລົດ-ພາກບັງຄັບ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ພິເສດ-ລົດ-ພາກສະໝັກໃຈ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ-ອັກຄີໄພ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ-ຂົນສົ່ງ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ- ອຫ ສ່ວນບຸກຄົນ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ-ສຸຂະພາບ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ-ທ່ອງທ່ຽວ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ-ຊັບສິນ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ- ຄສ ຮອບດ້ານ ອກ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ-ວິສະວະກຳ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ-ສິນເຊື່ອ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ຕາມພັນທະ- ຄສ ອື່ນໆ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ-ລົດ-ພາກບັງຄັບ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ-ລົດ-ພາກສະໝັກໃຈ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ-ອັກຄີໄພ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ-ຂົນສົ່ງ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ- ອຫ ສ່ວນບຸກຄົນ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ-ສຸຂະພາບ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ-ທ່ອງທ່ຽວ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ-ຊັບສິນ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ- ຄສ ຮອບດ້ານ ອກ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ-ວິສະວະກຳ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ-ສິນເຊື່ອ</t>
+  </si>
+  <si>
+    <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ- ຄສ ອື່ນໆ</t>
   </si>
 </sst>
 </file>
@@ -529,7 +767,7 @@
   <numFmts count="1">
     <numFmt numFmtId="187" formatCode="yyyymmdd"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,6 +822,24 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Phetsarath OT"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -642,7 +898,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -667,6 +923,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1003,20 +1263,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374CF59C-3341-4B17-A388-333F1CF3289F}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.19921875" customWidth="1"/>
-    <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" customWidth="1"/>
+    <col min="6" max="6" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.69921875" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>11</v>
       </c>
@@ -1051,7 +1311,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
@@ -1086,7 +1346,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1121,9 +1381,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{302E2BFD-2522-4A2C-8597-8B0E1A0E78FB}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,7 +1421,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -1199,7 +1459,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1229,4 +1489,343 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB66F36-C64B-401D-B19E-5DCE5D9D2041}">
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="3" max="3" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.9140625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="54.83203125" style="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="14">
+        <v>1618.07</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="14">
+        <v>1618.08</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="14">
+        <v>1618.09</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E5" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E8" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E9" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E10" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E11" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E12" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E13" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E14" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E15" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E17" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E18" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E19" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E20" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E21" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E22" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E23" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E24" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E25" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E26" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E27" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E28" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E29" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E30" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E31" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E32" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E33" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E34" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E37" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Template Import/AR Claim RE Template Service.xlsx
+++ b/Template Import/AR Claim RE Template Service.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\MSIGSX\Template Import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MSIGSX\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A535AD3F-0C26-4150-86BC-B44AB01F7082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E2C21C-7408-4E0D-A645-9FED653A6921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E44AA624-969E-4C5F-BCC1-7F47ABB06A31}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="13656" xr2:uid="{E44AA624-969E-4C5F-BCC1-7F47ABB06A31}"/>
   </bookViews>
   <sheets>
     <sheet name="Head" sheetId="2" r:id="rId1"/>
@@ -493,9 +493,6 @@
     <t>DocCur</t>
   </si>
   <si>
-    <t>AcctCode</t>
-  </si>
-  <si>
     <t>Series</t>
   </si>
   <si>
@@ -758,6 +755,9 @@
   </si>
   <si>
     <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ- ຄສ ອື່ນໆ</t>
+  </si>
+  <si>
+    <t>AccountingCode</t>
   </si>
 </sst>
 </file>
@@ -898,7 +898,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -928,6 +928,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1263,25 +1264,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374CF59C-3341-4B17-A388-333F1CF3289F}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.9140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.1640625" customWidth="1"/>
-    <col min="6" max="6" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.19921875" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>15</v>
@@ -1308,15 +1309,15 @@
         <v>22</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>15</v>
@@ -1343,10 +1344,10 @@
         <v>22</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1354,7 +1355,7 @@
         <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3">
         <v>20260624</v>
@@ -1366,10 +1367,10 @@
         <v>20260624</v>
       </c>
       <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
         <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1381,9 +1382,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{302E2BFD-2522-4A2C-8597-8B0E1A0E78FB}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="12" max="12" width="12.3984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1418,10 +1422,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.4">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -1456,10 +1460,10 @@
         <v>10</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1467,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
         <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
       </c>
       <c r="H3">
         <v>200000</v>
@@ -1479,10 +1483,10 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s">
         <v>30</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1494,334 +1498,335 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB66F36-C64B-401D-B19E-5DCE5D9D2041}">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.9140625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="54.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.8984375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="54.796875" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="14">
         <v>1618.07</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>35</v>
-      </c>
       <c r="E2" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="14">
         <v>1618.08</v>
       </c>
-      <c r="B3" t="s">
-        <v>27</v>
+      <c r="B3" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="14">
         <v>1618.09</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>38</v>
-      </c>
       <c r="E4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E5" s="14" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E6" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F6" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E6" s="14" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E7" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F7" s="13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E7" s="14" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F8" s="13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E8" s="14" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E9" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F9" s="13" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E9" s="14" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E10" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F10" s="13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E10" s="14" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F11" s="13" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E11" s="14" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F12" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E12" s="14" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E13" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F13" s="13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E13" s="14" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E14" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E14" s="14" t="s">
+      <c r="F14" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E15" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F15" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E15" s="14" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E16" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E16" s="14" t="s">
+      <c r="F16" s="13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E17" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F17" s="13" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E17" s="14" t="s">
+    <row r="18" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E18" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F18" s="13" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E18" s="14" t="s">
+    <row r="19" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E19" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F19" s="13" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E19" s="14" t="s">
+    <row r="20" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E20" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F20" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E20" s="14" t="s">
+    <row r="21" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E21" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F21" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E21" s="14" t="s">
+    <row r="22" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E22" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F22" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E22" s="14" t="s">
+    <row r="23" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E23" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F23" s="13" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E23" s="14" t="s">
+    <row r="24" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E24" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F24" s="13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E24" s="14" t="s">
+    <row r="25" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E25" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F25" s="13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E25" s="14" t="s">
+    <row r="26" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E26" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F26" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E26" s="14" t="s">
+    <row r="27" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E27" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F27" s="13" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E27" s="14" t="s">
+    <row r="28" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E28" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F28" s="13" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E28" s="14" t="s">
+    <row r="29" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E29" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F29" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E29" s="14" t="s">
+    <row r="30" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E30" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F30" s="13" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="30" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E30" s="14" t="s">
+    <row r="31" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E31" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F31" s="13" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E31" s="14" t="s">
+    <row r="32" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E32" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F32" s="13" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E32" s="14" t="s">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E33" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F33" s="13" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E33" s="14" t="s">
+    <row r="34" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E34" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F34" s="13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E34" s="14" t="s">
+    <row r="35" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E35" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="F35" s="13" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E35" s="14" t="s">
+    <row r="36" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E36" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="13" t="s">
+      <c r="F36" s="13" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E36" s="14" t="s">
+    <row r="37" spans="5:6" x14ac:dyDescent="0.4">
+      <c r="E37" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F37" s="13" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="5:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E37" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Template Import/AR Claim RE Template Service.xlsx
+++ b/Template Import/AR Claim RE Template Service.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\MSIGSX\Template Import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A535AD3F-0C26-4150-86BC-B44AB01F7082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAD2D92-EC1E-416C-8618-4AD9CDE6BABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E44AA624-969E-4C5F-BCC1-7F47ABB06A31}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E44AA624-969E-4C5F-BCC1-7F47ABB06A31}"/>
   </bookViews>
   <sheets>
     <sheet name="Head" sheetId="2" r:id="rId1"/>
@@ -419,7 +419,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="115">
   <si>
     <t>ParentKey</t>
   </si>
@@ -758,6 +758,12 @@
   </si>
   <si>
     <t>ສິນທົດແທນ ປກພ ຮຽກຄືນ- ປກພ ຕໍ່-ສັນຍາ ປກພ ຕໍ່ອື່ນໆ- ຄສ ອື່ນໆ</t>
+  </si>
+  <si>
+    <t>CHANNEL</t>
+  </si>
+  <si>
+    <t>604.60</t>
   </si>
 </sst>
 </file>
@@ -898,7 +904,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -926,6 +932,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1263,20 +1272,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374CF59C-3341-4B17-A388-333F1CF3289F}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.9140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.1640625" customWidth="1"/>
-    <col min="6" max="6" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.19921875" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
         <v>11</v>
       </c>
@@ -1311,7 +1320,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
@@ -1346,7 +1355,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1370,6 +1379,9 @@
       </c>
       <c r="I3" t="s">
         <v>28</v>
+      </c>
+      <c r="K3">
+        <v>222222</v>
       </c>
     </row>
   </sheetData>
@@ -1381,9 +1393,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{302E2BFD-2522-4A2C-8597-8B0E1A0E78FB}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="11" max="11" width="13.19921875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="16.2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1421,7 +1436,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="16.2" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -1459,7 +1474,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1493,23 +1508,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB66F36-C64B-401D-B19E-5DCE5D9D2041}">
-  <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="3" max="3" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.9140625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="54.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" customWidth="1"/>
+    <col min="3" max="3" width="41.296875" customWidth="1"/>
+    <col min="5" max="5" width="13.8984375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="54.796875" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.5">
       <c r="B1" t="s">
         <v>39</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="G1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A2" s="14">
         <v>1618.07</v>
       </c>
@@ -1526,15 +1545,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A3" s="14">
         <v>1618.08</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>42</v>
@@ -1543,15 +1562,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A4" s="14">
         <v>1618.09</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>43</v>
@@ -1560,7 +1579,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E5" s="14" t="s">
         <v>44</v>
       </c>
@@ -1568,7 +1587,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E6" s="14" t="s">
         <v>45</v>
       </c>
@@ -1576,7 +1595,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E7" s="14" t="s">
         <v>46</v>
       </c>
@@ -1584,7 +1603,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E8" s="14" t="s">
         <v>47</v>
       </c>
@@ -1592,7 +1611,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E9" s="14" t="s">
         <v>48</v>
       </c>
@@ -1600,7 +1619,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E10" s="14" t="s">
         <v>49</v>
       </c>
@@ -1608,7 +1627,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E11" s="14" t="s">
         <v>50</v>
       </c>
@@ -1616,7 +1635,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E12" s="14" t="s">
         <v>51</v>
       </c>
@@ -1624,7 +1643,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E13" s="14" t="s">
         <v>52</v>
       </c>
@@ -1632,7 +1651,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E14" s="14" t="s">
         <v>53</v>
       </c>
@@ -1640,7 +1659,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E15" s="14" t="s">
         <v>54</v>
       </c>
@@ -1648,7 +1667,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
       <c r="E16" s="14" t="s">
         <v>55</v>
       </c>
@@ -1656,7 +1675,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E17" s="14" t="s">
         <v>56</v>
       </c>
@@ -1664,7 +1683,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E18" s="14" t="s">
         <v>57</v>
       </c>
@@ -1672,7 +1691,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E19" s="14" t="s">
         <v>58</v>
       </c>
@@ -1680,7 +1699,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E20" s="14" t="s">
         <v>59</v>
       </c>
@@ -1688,7 +1707,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E21" s="14" t="s">
         <v>60</v>
       </c>
@@ -1696,7 +1715,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E22" s="14" t="s">
         <v>61</v>
       </c>
@@ -1704,7 +1723,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E23" s="14" t="s">
         <v>62</v>
       </c>
@@ -1712,7 +1731,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E24" s="14" t="s">
         <v>63</v>
       </c>
@@ -1720,7 +1739,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E25" s="14" t="s">
         <v>64</v>
       </c>
@@ -1728,7 +1747,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E26" s="14" t="s">
         <v>65</v>
       </c>
@@ -1736,7 +1755,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E27" s="14" t="s">
         <v>66</v>
       </c>
@@ -1744,7 +1763,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E28" s="14" t="s">
         <v>67</v>
       </c>
@@ -1752,7 +1771,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E29" s="14" t="s">
         <v>68</v>
       </c>
@@ -1760,7 +1779,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="30" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E30" s="14" t="s">
         <v>69</v>
       </c>
@@ -1768,7 +1787,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E31" s="14" t="s">
         <v>70</v>
       </c>
@@ -1776,7 +1795,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E32" s="14" t="s">
         <v>71</v>
       </c>
@@ -1784,7 +1803,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E33" s="14" t="s">
         <v>72</v>
       </c>
@@ -1792,7 +1811,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E34" s="14" t="s">
         <v>73</v>
       </c>
@@ -1800,7 +1819,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E35" s="14" t="s">
         <v>74</v>
       </c>
@@ -1808,7 +1827,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E36" s="14" t="s">
         <v>75</v>
       </c>
@@ -1816,12 +1835,27 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="5:6" x14ac:dyDescent="0.5">
       <c r="E37" s="14" t="s">
         <v>76</v>
       </c>
       <c r="F37" s="13" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="5:6" x14ac:dyDescent="0.5">
+      <c r="E38" s="15">
+        <v>604.59</v>
+      </c>
+    </row>
+    <row r="39" spans="5:6" x14ac:dyDescent="0.5">
+      <c r="E39" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="5:6" x14ac:dyDescent="0.5">
+      <c r="E40" s="15">
+        <v>604.61</v>
       </c>
     </row>
   </sheetData>
